--- a/nyc_taxi_analysis/07_summary/metrics.xlsx
+++ b/nyc_taxi_analysis/07_summary/metrics.xlsx
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9355</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="12">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>45751</v>
+        <v>47668</v>
       </c>
     </row>
     <row r="22">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6854</v>
+        <v>7045</v>
       </c>
     </row>
     <row r="23">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>95.89100000000001</v>
+        <v>109.287</v>
       </c>
     </row>
   </sheetData>
